--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:21</t>
+    <t xml:space="preserve">2026-09-10 01:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:35</t>
+    <t xml:space="preserve">2026-09-18 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:31</t>
+    <t xml:space="preserve">2026-09-23 15:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:36</t>
+    <t xml:space="preserve">2026-10-05 16:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -970,7 +970,7 @@
         <v>57.69</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>101</v>
+        <v>101.01</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>109.59</v>
